--- a/excel/Excel_Master_Report_Latest.xlsx
+++ b/excel/Excel_Master_Report_Latest.xlsx
@@ -923,7 +923,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>18.10.2026 kl. 17:08</t>
+          <t>18.10.2026 kl. 17:19</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>SHA-256: 1eb63ca16ff425abfb0d2b4f8cbda026e4be099841ab8916bf6e0fc84ddfcd58</t>
+          <t>SHA-256: 6e434ee569a69d33f58280989ed05203c8ccc95986472886a0998a061bcb68c1</t>
         </is>
       </c>
     </row>
